--- a/danielaybruno/danielaybruno.xlsx
+++ b/danielaybruno/danielaybruno.xlsx
@@ -5,7 +5,9 @@
   <sheets>
     <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$C$234</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
@@ -22,22 +24,1069 @@
     <t>Pases Asignados</t>
   </si>
   <si>
+    <t>Adith Zumaeta</t>
+  </si>
+  <si>
+    <t>Jhonny Quinteros</t>
+  </si>
+  <si>
+    <t>Adolfo Arevalo</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Adrian Rios Rondona</t>
+  </si>
+  <si>
+    <t>Sheryl Medina</t>
+  </si>
+  <si>
+    <t>Alejandra Castillo</t>
+  </si>
+  <si>
+    <t>Rodrigo Amasifuen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alejandro Lara </t>
+  </si>
+  <si>
+    <t>Alejandro Medina</t>
+  </si>
+  <si>
+    <t>Hilka Perez</t>
+  </si>
+  <si>
+    <t>Alexandra  Wong</t>
+  </si>
+  <si>
+    <t>Jose Luis Camero</t>
+  </si>
+  <si>
+    <t>Alexia Rios Garcia</t>
+  </si>
+  <si>
+    <t>Omar Murillo</t>
+  </si>
+  <si>
+    <t>Alfredo Kong</t>
+  </si>
+  <si>
+    <t>Rosa Chin Chau</t>
+  </si>
+  <si>
+    <t>Alonso Garcia Orosco</t>
+  </si>
+  <si>
+    <t>Alessa Guerrero</t>
+  </si>
+  <si>
+    <t>Alonso Mansilla</t>
+  </si>
+  <si>
+    <t>Ana Paula Tamayo</t>
+  </si>
+  <si>
+    <t>Daniel Cuentas</t>
+  </si>
+  <si>
+    <t>Andrea Ponce Romero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea Villareal </t>
+  </si>
+  <si>
+    <t>Axel Quiñe</t>
+  </si>
+  <si>
+    <t>Karla Rubio</t>
+  </si>
+  <si>
+    <t>Blanca Diaz</t>
+  </si>
+  <si>
+    <t>Brenda Pedreschi</t>
+  </si>
+  <si>
+    <t>Miguel Angel Wong</t>
+  </si>
+  <si>
+    <t>Brigitte Stamenovic</t>
+  </si>
+  <si>
+    <t>Sebastian Salazar</t>
+  </si>
+  <si>
+    <t>Bruno Galvéz</t>
+  </si>
+  <si>
+    <t>Bryan Gonzales</t>
+  </si>
+  <si>
+    <t>Gisella  Pinedo</t>
+  </si>
+  <si>
+    <t>Camila Galvéz  Rios</t>
+  </si>
+  <si>
+    <t>Jorge Valdez</t>
+  </si>
+  <si>
+    <t>Carlos del Aguila</t>
+  </si>
+  <si>
+    <t>Carlos del Aguila Junior</t>
+  </si>
+  <si>
+    <t>Carola Cobos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Mendoza </t>
+  </si>
+  <si>
+    <t>Carlos Rios Trigozo</t>
+  </si>
+  <si>
+    <t>Deysi Cortez Mendoza</t>
+  </si>
+  <si>
+    <t>Carlos Rojas</t>
+  </si>
+  <si>
+    <t>Silvia del Aguila</t>
+  </si>
+  <si>
+    <t>Carlos Santillan</t>
+  </si>
+  <si>
+    <t>Karina Sanchez</t>
+  </si>
+  <si>
+    <t>Carlos Santillán</t>
+  </si>
+  <si>
+    <t>Estephany Mori</t>
+  </si>
+  <si>
+    <t>Carlos Toribio</t>
+  </si>
+  <si>
+    <t>Julia Elvira</t>
+  </si>
+  <si>
+    <t>Caro Zumaeta</t>
+  </si>
+  <si>
+    <t>Tomas Said</t>
+  </si>
+  <si>
+    <t>Carola Santillan</t>
+  </si>
+  <si>
+    <t>Carolina Gomez</t>
+  </si>
+  <si>
+    <t>Cesar Cucho</t>
+  </si>
+  <si>
+    <t>Karen Zumaeta</t>
+  </si>
+  <si>
+    <t>César Espinoza</t>
+  </si>
+  <si>
+    <t>Valeria Valles</t>
+  </si>
+  <si>
+    <t>César Ramos</t>
+  </si>
+  <si>
+    <t>César Reategui</t>
+  </si>
+  <si>
+    <t>Elia Garcia</t>
+  </si>
+  <si>
+    <t>Cesar Rios</t>
+  </si>
+  <si>
+    <t>Julieth Silva</t>
+  </si>
+  <si>
+    <t>Cesar Zumaeta</t>
+  </si>
+  <si>
+    <t>Yary Valencia</t>
+  </si>
+  <si>
+    <t>Cindy Reategui</t>
+  </si>
+  <si>
+    <t>Claudia Hermoza</t>
+  </si>
+  <si>
+    <t>Claudia Morán</t>
+  </si>
+  <si>
+    <t>Claudia Silva Estrada</t>
+  </si>
+  <si>
+    <t>Cliver Rios Zumaeta</t>
+  </si>
+  <si>
+    <t>Delia Vasquez</t>
+  </si>
+  <si>
+    <t>Cristhian Rios Lozano</t>
+  </si>
+  <si>
+    <t>Brunella Chong</t>
+  </si>
+  <si>
+    <t>Daniel Melendez Lozano</t>
+  </si>
+  <si>
+    <t>Daniel Vásquez</t>
+  </si>
+  <si>
+    <t>Valentina Mesias</t>
+  </si>
+  <si>
+    <t>David Medina</t>
+  </si>
+  <si>
+    <t>Sheyla Hoyos</t>
+  </si>
+  <si>
+    <t>Diego Santillan</t>
+  </si>
+  <si>
+    <t>Juliana Segura</t>
+  </si>
+  <si>
+    <t>Diego Zumaeta</t>
+  </si>
+  <si>
+    <t>Zoila Saldaña</t>
+  </si>
+  <si>
+    <t>Ediberto Reategui</t>
+  </si>
+  <si>
+    <t>Reggina Reveggino</t>
+  </si>
+  <si>
+    <t>Eleneonor Moncayo</t>
+  </si>
+  <si>
+    <t>Elia Rios</t>
+  </si>
+  <si>
+    <t>Edward Michuy</t>
+  </si>
+  <si>
+    <t>Elke Ramirez</t>
+  </si>
+  <si>
+    <t>Elva Ruiz</t>
+  </si>
+  <si>
+    <t>Angel Cuya</t>
+  </si>
+  <si>
+    <t>Emerson Zumaeta</t>
+  </si>
+  <si>
+    <t>Hellen Rodrigues</t>
+  </si>
+  <si>
+    <t>Emil Reategui</t>
+  </si>
+  <si>
+    <t>Valery Pinzas</t>
+  </si>
+  <si>
+    <t>Erick Melendez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erick Santillan </t>
+  </si>
+  <si>
+    <t>Esteban Obed</t>
+  </si>
+  <si>
+    <t>Fabio Guitierrez</t>
+  </si>
+  <si>
+    <t>Mariana Loli</t>
+  </si>
+  <si>
+    <t>Fabrizzio Marin</t>
+  </si>
+  <si>
+    <t>Fabrizzio Rios Canani</t>
+  </si>
+  <si>
+    <t>Leslie Arce</t>
+  </si>
+  <si>
+    <t>Fernanda Linares</t>
+  </si>
+  <si>
+    <t>Adriana Linares</t>
+  </si>
+  <si>
+    <t>Fernando Tafur</t>
+  </si>
+  <si>
+    <t>Fiorella Rodriguez Sandoval</t>
+  </si>
+  <si>
+    <t>Florencia Hung</t>
+  </si>
+  <si>
+    <t>Francisco Zumaeta</t>
+  </si>
+  <si>
+    <t>Luisa Romero</t>
+  </si>
+  <si>
+    <t>Frank Gonzales</t>
+  </si>
+  <si>
+    <t>Cinthya Palomino</t>
+  </si>
+  <si>
+    <t>Gabriel Mazzini</t>
+  </si>
+  <si>
+    <t>German Rios Rios</t>
+  </si>
+  <si>
+    <t>Gianpiero Olaya</t>
+  </si>
+  <si>
+    <t>Gilson  Amasifuen</t>
+  </si>
+  <si>
+    <t>Giovanni Ponce Saavedra</t>
+  </si>
+  <si>
+    <t>Jessica Chong , Carlos Ponce Chong</t>
+  </si>
+  <si>
+    <t>Gladys Zumaeta</t>
+  </si>
+  <si>
+    <t>Gloria Aguayo</t>
+  </si>
+  <si>
+    <t>Carlos Ruiz</t>
+  </si>
+  <si>
+    <t>Grace  Pérez Garcia</t>
+  </si>
+  <si>
+    <t>Gretty Garcia Hidalgo</t>
+  </si>
+  <si>
+    <t>Hector Figueroa Zumaeta</t>
+  </si>
+  <si>
+    <t>Mafer Canales</t>
+  </si>
+  <si>
+    <t>Henry Figueroa Zumaeta</t>
+  </si>
+  <si>
+    <t>Adriana Córdova</t>
+  </si>
+  <si>
+    <t>Iraida Trigozo del Aguila</t>
+  </si>
+  <si>
+    <t>Isaac Coriat</t>
+  </si>
+  <si>
+    <t>Janeth Caballero</t>
+  </si>
+  <si>
+    <t>Isac Maldonado</t>
+  </si>
+  <si>
+    <t>Ivan Zumaeta</t>
+  </si>
+  <si>
+    <t>Rosa Arevalo</t>
+  </si>
+  <si>
+    <t>Janeth Escobar</t>
+  </si>
+  <si>
+    <t>Jeanpierre Aguayo</t>
+  </si>
+  <si>
+    <t>Jessica Maldonado</t>
+  </si>
+  <si>
+    <t>Cesar Wong</t>
+  </si>
+  <si>
+    <t>Jesus Enrique Arevalo</t>
+  </si>
+  <si>
+    <t>Karen Documet, Joaquim Arevalo</t>
+  </si>
+  <si>
+    <t>Jhonathan Hidalgo</t>
+  </si>
+  <si>
+    <t>Alessandra Galvéz Rios</t>
+  </si>
+  <si>
+    <t>Jin Saldaña Kanan</t>
+  </si>
+  <si>
+    <t>Jisbert Paredes</t>
+  </si>
+  <si>
+    <t>Gladys Cardenas</t>
+  </si>
+  <si>
+    <t>Joaquim Flores</t>
+  </si>
+  <si>
+    <t>Joaquim Villareal</t>
+  </si>
+  <si>
+    <t>John Arevalo</t>
+  </si>
+  <si>
+    <t>Iliana Bocanegra</t>
+  </si>
+  <si>
+    <t>Jordy Pereira</t>
+  </si>
+  <si>
+    <t>Shania Alarcón</t>
+  </si>
+  <si>
+    <t>Jorge Rios Hoyos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Canani </t>
+  </si>
+  <si>
+    <t>Jorge Velasquez</t>
+  </si>
+  <si>
+    <t>Ana Arevalo</t>
+  </si>
+  <si>
+    <t>Jose  Zumaeta</t>
+  </si>
+  <si>
+    <t>Ellana Souza Stirling</t>
+  </si>
+  <si>
+    <t>Jose Antonio Meoño</t>
+  </si>
+  <si>
+    <t>Susan Pulido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jose Antonio Napanga </t>
+  </si>
+  <si>
+    <t>Jose Luis Garcia Ramirez</t>
+  </si>
+  <si>
+    <t>Malena Orosco La Vera, Maria Alejandra Garcia Orosco</t>
+  </si>
+  <si>
+    <t>Joseph Trigozo</t>
+  </si>
+  <si>
+    <t>Josias Lozano Fidalgo</t>
+  </si>
+  <si>
+    <t>Maria del Aguila Sanchez</t>
+  </si>
+  <si>
+    <t>Juan Alejandro Gomez</t>
+  </si>
+  <si>
+    <t>Jimena Calmet</t>
+  </si>
+  <si>
+    <t>Juan Diego Diaz Grandez</t>
+  </si>
+  <si>
+    <t>Julio Ramirez Macedo</t>
+  </si>
+  <si>
+    <t>Rosa Paredes Piña, Julio Abel Ramirez</t>
+  </si>
+  <si>
+    <t>Karina Morey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos </t>
+  </si>
+  <si>
+    <t>Kevin Rios</t>
+  </si>
+  <si>
+    <t>Estrella Torres</t>
+  </si>
+  <si>
+    <t>Lily Pérez Garcia</t>
+  </si>
+  <si>
+    <t>Abdellah Ammouri</t>
+  </si>
+  <si>
+    <t>Linda Sangama</t>
+  </si>
+  <si>
+    <t>Javier Romo</t>
+  </si>
+  <si>
+    <t>Liz Cheril Torres Reategui</t>
+  </si>
+  <si>
+    <t>Alison Mori</t>
+  </si>
+  <si>
+    <t>Liz Vargas</t>
+  </si>
+  <si>
+    <t>Ruben Trigozo</t>
+  </si>
+  <si>
+    <t>Lluis Dalmau</t>
+  </si>
+  <si>
+    <t>Lluis Dalmau Mendoza, Quim Dalmau Mendoza, Ariadna Dalmau Mendoza</t>
+  </si>
+  <si>
+    <t>Lorena Morey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrique </t>
+  </si>
+  <si>
+    <t>Lucas Zumaeta</t>
+  </si>
+  <si>
+    <t>Cristina Mattos</t>
+  </si>
+  <si>
+    <t>Lucecita Pretell</t>
+  </si>
+  <si>
+    <t>Lucia Rojas</t>
+  </si>
+  <si>
+    <t>Lucia Valdiviezo</t>
+  </si>
+  <si>
+    <t>Luciana Fajardo Sandy</t>
+  </si>
+  <si>
+    <t>Luis Angel Samaniego</t>
+  </si>
+  <si>
+    <t>Luis Garcia Hidalgo</t>
+  </si>
+  <si>
+    <t>Enith Ramirez Macedo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis Gómez </t>
+  </si>
+  <si>
+    <t>Solange Noriega</t>
+  </si>
+  <si>
+    <t>Luis Guimaraes</t>
+  </si>
+  <si>
+    <t>Pilar Meza</t>
+  </si>
+  <si>
+    <t>Luis Mori Reategui</t>
+  </si>
+  <si>
+    <t>Luis Rios Trigozo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erika Garcia Ramirez </t>
+  </si>
+  <si>
+    <t>Luis Tamayo</t>
+  </si>
+  <si>
+    <t>Blanca Rios</t>
+  </si>
+  <si>
+    <t>Luz Ley Guiudichi</t>
+  </si>
+  <si>
+    <t>Manuel Sotelo</t>
+  </si>
+  <si>
+    <t>Hilda Ruiz</t>
+  </si>
+  <si>
+    <t>Manuel Zumaeta</t>
+  </si>
+  <si>
+    <t>Christianny De Sena</t>
+  </si>
+  <si>
+    <t>Marcela Zumaeta</t>
+  </si>
+  <si>
+    <t>Allan V.Bastos</t>
+  </si>
+  <si>
+    <t>Marcelo Campos</t>
+  </si>
+  <si>
+    <t>Beatriz Zumaeta</t>
+  </si>
+  <si>
+    <t>Marcelo Zumaeta</t>
+  </si>
+  <si>
+    <t>Anita Herrera</t>
+  </si>
+  <si>
+    <t>Marcia Chavez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Novoa </t>
+  </si>
+  <si>
+    <t>Vanessa  Mena</t>
+  </si>
+  <si>
+    <t>Maria Elena Rios Trigozo</t>
+  </si>
+  <si>
+    <t>Diego Romero Rios, Lucia Romero Rios</t>
+  </si>
+  <si>
+    <t>Maria Elena Rios Zumaeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Rios </t>
+  </si>
+  <si>
+    <t>Mariana Bocanegra</t>
+  </si>
+  <si>
+    <t>Marino Lozano</t>
+  </si>
+  <si>
+    <t>Chepita Mori</t>
+  </si>
+  <si>
+    <t>Mario Arroyo</t>
+  </si>
+  <si>
+    <t>Mario Berghusen</t>
+  </si>
+  <si>
+    <t>Mario Flores</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
+  </si>
+  <si>
+    <t>Marita Arevalo</t>
+  </si>
+  <si>
+    <t>Marta Patricia Arevalo</t>
+  </si>
+  <si>
+    <t>Martin Sangama</t>
+  </si>
+  <si>
+    <t>Mauricio Choy</t>
+  </si>
+  <si>
+    <t>Melanie del Castillo</t>
+  </si>
+  <si>
+    <t>Melina Marquilla</t>
+  </si>
+  <si>
+    <t>Michelle Bergelund</t>
+  </si>
+  <si>
+    <t>Michelle Ponce Chong</t>
+  </si>
+  <si>
+    <t>Maximilian Kadzioch</t>
+  </si>
+  <si>
+    <t>Miguel Galvéz Tello</t>
+  </si>
+  <si>
+    <t>Margarita Rios Trigozo, Facundo Galvéz Rios</t>
+  </si>
+  <si>
+    <t>Miguel Santillan</t>
+  </si>
+  <si>
+    <t>Karen Goicochea</t>
+  </si>
+  <si>
+    <t>Miguel Zurita</t>
+  </si>
+  <si>
+    <t>Milagros Arevalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milena vela  </t>
+  </si>
+  <si>
+    <t>Moi Merino Morey</t>
+  </si>
+  <si>
+    <t>Carmen Padilla</t>
+  </si>
+  <si>
+    <t>Monica Lozano del Aguila</t>
+  </si>
+  <si>
+    <t>Mosiy  Zumaeta</t>
+  </si>
+  <si>
+    <t>Carlos Noriega</t>
+  </si>
+  <si>
+    <t>Nancy Macedo</t>
+  </si>
+  <si>
+    <t>Nancy Zumaeta</t>
+  </si>
+  <si>
+    <t>Nelly Villarcorta</t>
+  </si>
+  <si>
+    <t>Pastor Zumaeta</t>
+  </si>
+  <si>
+    <t>Nene Sangama</t>
+  </si>
+  <si>
+    <t>Ericka Flores, Diana Sangama</t>
+  </si>
+  <si>
+    <t>Nery Zumaeta</t>
+  </si>
+  <si>
+    <t>Roger Arevalo</t>
+  </si>
+  <si>
+    <t>Nicolas Ramos</t>
+  </si>
+  <si>
+    <t>Nicolas Valle</t>
+  </si>
+  <si>
+    <t>Renata Rojo</t>
+  </si>
+  <si>
+    <t>Nicole Alarcon</t>
+  </si>
+  <si>
+    <t>Nicolle Ramirez Santillana</t>
+  </si>
+  <si>
+    <t>Oscar Gomez</t>
+  </si>
+  <si>
+    <t>Juana Morey</t>
+  </si>
+  <si>
+    <t>Oscar Pelaez</t>
+  </si>
+  <si>
+    <t>Jeny Reategui</t>
+  </si>
+  <si>
+    <t>Pamela Chu Noriega</t>
+  </si>
+  <si>
+    <t>Ivana Mendoza, Valeria Mendoza</t>
+  </si>
+  <si>
+    <t>Paola Rios</t>
+  </si>
+  <si>
+    <t>Oscar Escudero</t>
+  </si>
+  <si>
+    <t>Paolo Figueroa Zumaeta</t>
+  </si>
+  <si>
+    <t>Fabiana Finocchiaro</t>
+  </si>
+  <si>
+    <t>Paquita Lozano</t>
+  </si>
+  <si>
+    <t>Kiler Coral</t>
+  </si>
+  <si>
+    <t>Patricia Contreras</t>
+  </si>
+  <si>
+    <t>Patricia Tello</t>
+  </si>
+  <si>
+    <t>Paul Rios</t>
+  </si>
+  <si>
+    <t>Claudia Amaya</t>
+  </si>
+  <si>
+    <t>Pedro Quiquen</t>
+  </si>
+  <si>
+    <t>Carolina Tuesta</t>
+  </si>
+  <si>
+    <t>Percy Ponce Saavedra</t>
+  </si>
+  <si>
+    <t>Gretell Romero</t>
+  </si>
+  <si>
+    <t>Pierre Barté</t>
+  </si>
+  <si>
+    <t>Melissa Garfias</t>
+  </si>
+  <si>
+    <t>Raul Sotelo</t>
+  </si>
+  <si>
+    <t>Fabita de Sotelo</t>
+  </si>
+  <si>
+    <t>Remigio Zumaeta</t>
+  </si>
+  <si>
+    <t>Renato Fernandini</t>
+  </si>
+  <si>
+    <t>Fernanda Cárdenas</t>
+  </si>
+  <si>
+    <t>Renzo Perez Rosas</t>
+  </si>
+  <si>
+    <t>Renzo Reategui Rey</t>
+  </si>
+  <si>
+    <t>Renzo Santillan</t>
+  </si>
+  <si>
+    <t>Antuane Reategui</t>
+  </si>
+  <si>
+    <t>Richer Rios Zumaeta</t>
+  </si>
+  <si>
+    <t>Elizabeth Alvarado</t>
+  </si>
+  <si>
+    <t>Rita Rios</t>
+  </si>
+  <si>
+    <t>Robert Cardenas</t>
+  </si>
+  <si>
+    <t>Rosmery Gonzales</t>
+  </si>
+  <si>
+    <t>Robinson Rios Zumaeta</t>
+  </si>
+  <si>
+    <t>Luisa Mori</t>
+  </si>
+  <si>
+    <t>Rodrigo Carrasco</t>
+  </si>
+  <si>
+    <t>Flavia Vega</t>
+  </si>
+  <si>
+    <t>Roger Lozano del Aguila</t>
+  </si>
+  <si>
+    <t>Alejandra Gonzales, Camila Lozano</t>
+  </si>
+  <si>
+    <t>Roger Maldonado</t>
+  </si>
+  <si>
+    <t>Mercedez Rodriguez</t>
+  </si>
+  <si>
+    <t>Rolando Lam</t>
+  </si>
+  <si>
+    <t>Milagros Gardini</t>
+  </si>
+  <si>
+    <t>Rolando Macedo</t>
+  </si>
+  <si>
+    <t>Alicia Arevalo</t>
+  </si>
+  <si>
+    <t>Rossana Corzano</t>
+  </si>
+  <si>
+    <t>Ivan Alarcon</t>
+  </si>
+  <si>
+    <t>Samantha Zavaleta</t>
+  </si>
+  <si>
+    <t>Oscar Calderon</t>
+  </si>
+  <si>
+    <t>Samir Florian</t>
+  </si>
+  <si>
+    <t>Sandra Alvarado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandra Rios </t>
+  </si>
+  <si>
+    <t>Rafael Lopez</t>
+  </si>
+  <si>
+    <t>Sandro Zavaleta</t>
+  </si>
+  <si>
+    <t>Noris Arevalo, Fatima Zavaleta</t>
+  </si>
+  <si>
+    <t>Sebastián Diaz Quiñe</t>
+  </si>
+  <si>
+    <t>Sebastian Saz</t>
+  </si>
+  <si>
     <t>Segundo Rios Zumaeta</t>
   </si>
   <si>
     <t>Rocio Lozano del Aguila</t>
   </si>
   <si>
-    <t>Cristhian Rios Lozano</t>
-  </si>
-  <si>
-    <t>Brunella Chong</t>
-  </si>
-  <si>
-    <t>Josias Lozano Fidalgo</t>
-  </si>
-  <si>
-    <t>Maria del Aguila Sanchez</t>
+    <t>Shade Rios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veronica Villacaba </t>
+  </si>
+  <si>
+    <t>Shirley Rios</t>
+  </si>
+  <si>
+    <t>Francisco Vermejo</t>
+  </si>
+  <si>
+    <t>Silvia Rios Gil</t>
+  </si>
+  <si>
+    <t>Silvia Saavedra</t>
+  </si>
+  <si>
+    <t>Sliver Ramirez</t>
+  </si>
+  <si>
+    <t>Sol Lozano</t>
+  </si>
+  <si>
+    <t>Stacy Moya</t>
+  </si>
+  <si>
+    <t>Cesar Sernaque</t>
+  </si>
+  <si>
+    <t>Stefano Saracco Reategui</t>
+  </si>
+  <si>
+    <t>Talia Rios</t>
+  </si>
+  <si>
+    <t>Talita Garcia</t>
+  </si>
+  <si>
+    <t>Marlon Olortegui Peralta</t>
+  </si>
+  <si>
+    <t>Tatiana Pérez- Clement</t>
+  </si>
+  <si>
+    <t>Arnaud Clement</t>
+  </si>
+  <si>
+    <t>Tato Reategui</t>
+  </si>
+  <si>
+    <t>Violeta Cortez, Alexandra Reategui, Gianluca Reategui</t>
+  </si>
+  <si>
+    <t>Teddy Ramirez Macedo</t>
+  </si>
+  <si>
+    <t>Tony Sotelo</t>
+  </si>
+  <si>
+    <t>Madeleine Guiterrez</t>
+  </si>
+  <si>
+    <t>Tricia Garcia Ramirez</t>
+  </si>
+  <si>
+    <t>Valentina Ponce Romero</t>
+  </si>
+  <si>
+    <t>Lucas Camargo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valeria Aguirre </t>
+  </si>
+  <si>
+    <t>Valeria Rios</t>
+  </si>
+  <si>
+    <t>Valeria Sotelo</t>
+  </si>
+  <si>
+    <t>Mauricio Fernandez</t>
+  </si>
+  <si>
+    <t>Valerie Saire</t>
+  </si>
+  <si>
+    <t>Irving Espinoza</t>
+  </si>
+  <si>
+    <t>Valerie Stamenovic</t>
+  </si>
+  <si>
+    <t>Javier Gómez Bustamante</t>
   </si>
   <si>
     <t>Vanessa Lozano del Aguila</t>
@@ -46,1081 +1095,34 @@
     <t>Paul Alvarado, Joaquim Valenzuela</t>
   </si>
   <si>
-    <t>Monica Lozano del Aguila</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Roger Lozano del Aguila</t>
-  </si>
-  <si>
-    <t>Alejandra Gonzales, Camila Lozano</t>
-  </si>
-  <si>
-    <t>German Rios Rios</t>
-  </si>
-  <si>
-    <t>Robinson Rios Zumaeta</t>
-  </si>
-  <si>
-    <t>Luisa Mori</t>
-  </si>
-  <si>
-    <t>Maria Elena Rios Zumaeta</t>
-  </si>
-  <si>
-    <t>Luis Tamayo</t>
-  </si>
-  <si>
-    <t>Blanca Rios</t>
-  </si>
-  <si>
-    <t>Richer Rios Zumaeta</t>
-  </si>
-  <si>
-    <t>Elizabeth Alvarado</t>
-  </si>
-  <si>
-    <t>Cliver Rios Zumaeta</t>
-  </si>
-  <si>
-    <t>Delia Vasquez</t>
-  </si>
-  <si>
-    <t>Adith Zumaeta</t>
-  </si>
-  <si>
-    <t>Jhonny Quinteros</t>
-  </si>
-  <si>
-    <t>Daniel Melendez Lozano</t>
-  </si>
-  <si>
-    <t>Stacy Moya</t>
-  </si>
-  <si>
-    <t>Cesar Sernaque</t>
-  </si>
-  <si>
-    <t>Sol Lozano</t>
-  </si>
-  <si>
-    <t>Shade Rios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veronica Villacaba </t>
-  </si>
-  <si>
-    <t>Paola Rios</t>
-  </si>
-  <si>
-    <t>Oscar Escudero</t>
-  </si>
-  <si>
-    <t>Ana Paula Tamayo</t>
-  </si>
-  <si>
-    <t>Daniel Cuentas</t>
-  </si>
-  <si>
-    <t>Paul Rios</t>
-  </si>
-  <si>
-    <t>Claudia Amaya</t>
-  </si>
-  <si>
-    <t>Jeanpierre Aguayo</t>
-  </si>
-  <si>
-    <t>Gloria Aguayo</t>
-  </si>
-  <si>
-    <t>Carlos Ruiz</t>
-  </si>
-  <si>
-    <t>Talia Rios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Rios </t>
-  </si>
-  <si>
-    <t>Kevin Rios</t>
-  </si>
-  <si>
-    <t>Estrella Torres</t>
-  </si>
-  <si>
-    <t>Oscar Gomez</t>
-  </si>
-  <si>
-    <t>Carolina Gomez</t>
-  </si>
-  <si>
-    <t>Paolo Figueroa Zumaeta</t>
-  </si>
-  <si>
-    <t>Fabiana Finocchiaro</t>
-  </si>
-  <si>
-    <t>Henry Figueroa Zumaeta</t>
-  </si>
-  <si>
-    <t>Adriana Córdova</t>
-  </si>
-  <si>
-    <t>Hector Figueroa Zumaeta</t>
-  </si>
-  <si>
-    <t>Mafer Canales</t>
-  </si>
-  <si>
-    <t>Valeria Rios</t>
-  </si>
-  <si>
-    <t>Alexandra  Wong</t>
-  </si>
-  <si>
-    <t>Jose Luis Camero</t>
-  </si>
-  <si>
-    <t>Jessica Maldonado</t>
-  </si>
-  <si>
-    <t>Cesar Wong</t>
+    <t>Vanessa Vergara</t>
+  </si>
+  <si>
+    <t>Vida Zumaeta</t>
+  </si>
+  <si>
+    <t>Vivian Zumaeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Luis </t>
+  </si>
+  <si>
+    <t>Winston Jr Zumaeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lidici Pomin </t>
+  </si>
+  <si>
+    <t>Winston Zumaeta</t>
+  </si>
+  <si>
+    <t>Marta Moncayo</t>
   </si>
   <si>
     <t>Yuri Rios</t>
   </si>
   <si>
     <t>Montserrat Lopez</t>
-  </si>
-  <si>
-    <t>Shirley Rios</t>
-  </si>
-  <si>
-    <t>Francisco Vermejo</t>
-  </si>
-  <si>
-    <t>Patricia Contreras</t>
-  </si>
-  <si>
-    <t>Tony Sotelo</t>
-  </si>
-  <si>
-    <t>Madeleine Guiterrez</t>
-  </si>
-  <si>
-    <t>Manuel Sotelo</t>
-  </si>
-  <si>
-    <t>Hilda Ruiz</t>
-  </si>
-  <si>
-    <t>Raul Sotelo</t>
-  </si>
-  <si>
-    <t>Fabita de Sotelo</t>
-  </si>
-  <si>
-    <t>Carlos del Aguila</t>
-  </si>
-  <si>
-    <t>Carlos del Aguila Junior</t>
-  </si>
-  <si>
-    <t>Carola Cobos</t>
-  </si>
-  <si>
-    <t>Francisco Zumaeta</t>
-  </si>
-  <si>
-    <t>Luisa Romero</t>
-  </si>
-  <si>
-    <t>Winston Zumaeta</t>
-  </si>
-  <si>
-    <t>Marta Moncayo</t>
-  </si>
-  <si>
-    <t>Nancy Zumaeta</t>
-  </si>
-  <si>
-    <t>Eleneonor Moncayo</t>
-  </si>
-  <si>
-    <t>Cesar Zumaeta</t>
-  </si>
-  <si>
-    <t>Yary Valencia</t>
-  </si>
-  <si>
-    <t>Ivan Zumaeta</t>
-  </si>
-  <si>
-    <t>Rosa Arevalo</t>
-  </si>
-  <si>
-    <t>Mosiy  Zumaeta</t>
-  </si>
-  <si>
-    <t>Carlos Noriega</t>
-  </si>
-  <si>
-    <t>Marcela Zumaeta</t>
-  </si>
-  <si>
-    <t>Allan V.Bastos</t>
-  </si>
-  <si>
-    <t>Caro Zumaeta</t>
-  </si>
-  <si>
-    <t>Tomas Said</t>
-  </si>
-  <si>
-    <t>Jose  Zumaeta</t>
-  </si>
-  <si>
-    <t>Ellana Souza Stirling</t>
-  </si>
-  <si>
-    <t>Manuel Zumaeta</t>
-  </si>
-  <si>
-    <t>Christianny De Sena</t>
-  </si>
-  <si>
-    <t>Emerson Zumaeta</t>
-  </si>
-  <si>
-    <t>Hellen Rodrigues</t>
-  </si>
-  <si>
-    <t>Jisbert Paredes</t>
-  </si>
-  <si>
-    <t>Gladys Cardenas</t>
-  </si>
-  <si>
-    <t>Elia Rios</t>
-  </si>
-  <si>
-    <t>Edward Michuy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandra Rios </t>
-  </si>
-  <si>
-    <t>Rafael Lopez</t>
-  </si>
-  <si>
-    <t>Rita Rios</t>
-  </si>
-  <si>
-    <t>Mario Flores</t>
-  </si>
-  <si>
-    <t>Fiorella</t>
-  </si>
-  <si>
-    <t>Vida Zumaeta</t>
-  </si>
-  <si>
-    <t>Marcelo Zumaeta</t>
-  </si>
-  <si>
-    <t>Anita Herrera</t>
-  </si>
-  <si>
-    <t>Diego Zumaeta</t>
-  </si>
-  <si>
-    <t>Zoila Saldaña</t>
-  </si>
-  <si>
-    <t>Nery Zumaeta</t>
-  </si>
-  <si>
-    <t>Roger Arevalo</t>
-  </si>
-  <si>
-    <t>Cesar Rios</t>
-  </si>
-  <si>
-    <t>Julieth Silva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milena vela  </t>
-  </si>
-  <si>
-    <t>Karina Morey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos </t>
-  </si>
-  <si>
-    <t>Lorena Morey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enrique </t>
-  </si>
-  <si>
-    <t>Roger Maldonado</t>
-  </si>
-  <si>
-    <t>Mercedez Rodriguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jose Antonio Napanga </t>
-  </si>
-  <si>
-    <t>Vivian Zumaeta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Luis </t>
-  </si>
-  <si>
-    <t>Gladys Zumaeta</t>
-  </si>
-  <si>
-    <t>Lucas Zumaeta</t>
-  </si>
-  <si>
-    <t>Cristina Mattos</t>
-  </si>
-  <si>
-    <t>Cesar Cucho</t>
-  </si>
-  <si>
-    <t>Karen Zumaeta</t>
-  </si>
-  <si>
-    <t>Remigio Zumaeta</t>
-  </si>
-  <si>
-    <t>Winston Jr Zumaeta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lidici Pomin </t>
-  </si>
-  <si>
-    <t>Marcelo Campos</t>
-  </si>
-  <si>
-    <t>Beatriz Zumaeta</t>
-  </si>
-  <si>
-    <t>Luz Ley Guiudichi</t>
-  </si>
-  <si>
-    <t>Elke Ramirez</t>
-  </si>
-  <si>
-    <t>Nelly Villarcorta</t>
-  </si>
-  <si>
-    <t>Pastor Zumaeta</t>
-  </si>
-  <si>
-    <t>Renzo Santillan</t>
-  </si>
-  <si>
-    <t>Antuane Reategui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erick Santillan </t>
-  </si>
-  <si>
-    <t>Miguel Santillan</t>
-  </si>
-  <si>
-    <t>Karen Goicochea</t>
-  </si>
-  <si>
-    <t>Carola Santillan</t>
-  </si>
-  <si>
-    <t>Sandro Zavaleta</t>
-  </si>
-  <si>
-    <t>Noris Arevalo, Fatima Zavaleta</t>
-  </si>
-  <si>
-    <t>David Medina</t>
-  </si>
-  <si>
-    <t>Sheyla Hoyos</t>
-  </si>
-  <si>
-    <t>Marta Patricia Arevalo</t>
-  </si>
-  <si>
-    <t>Marita Arevalo</t>
-  </si>
-  <si>
-    <t>Nene Sangama</t>
-  </si>
-  <si>
-    <t>Ericka Flores, Diana Sangama</t>
-  </si>
-  <si>
-    <t>Ediberto Reategui</t>
-  </si>
-  <si>
-    <t>Reggina Reveggino</t>
-  </si>
-  <si>
-    <t>Luis Guimaraes</t>
-  </si>
-  <si>
-    <t>Pilar Meza</t>
-  </si>
-  <si>
-    <t>Rolando Macedo</t>
-  </si>
-  <si>
-    <t>Alicia Arevalo</t>
-  </si>
-  <si>
-    <t>Robert Cardenas</t>
-  </si>
-  <si>
-    <t>Rosmery Gonzales</t>
-  </si>
-  <si>
-    <t>César Reategui</t>
-  </si>
-  <si>
-    <t>Elia Garcia</t>
-  </si>
-  <si>
-    <t>Emil Reategui</t>
-  </si>
-  <si>
-    <t>Valery Pinzas</t>
-  </si>
-  <si>
-    <t>Cindy Reategui</t>
-  </si>
-  <si>
-    <t>Carlos Rojas</t>
-  </si>
-  <si>
-    <t>Silvia del Aguila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marco Novoa </t>
-  </si>
-  <si>
-    <t>Vanessa  Mena</t>
-  </si>
-  <si>
-    <t>John Arevalo</t>
-  </si>
-  <si>
-    <t>Iliana Bocanegra</t>
-  </si>
-  <si>
-    <t>Carlos Santillan</t>
-  </si>
-  <si>
-    <t>Karina Sanchez</t>
-  </si>
-  <si>
-    <t>Oscar Pelaez</t>
-  </si>
-  <si>
-    <t>Jeny Reategui</t>
-  </si>
-  <si>
-    <t>Ruben Trigozo</t>
-  </si>
-  <si>
-    <t>Jorge Velasquez</t>
-  </si>
-  <si>
-    <t>Ana Arevalo</t>
-  </si>
-  <si>
-    <t>Jose Antonio Meoño</t>
-  </si>
-  <si>
-    <t>Susan Pulido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis Gómez </t>
-  </si>
-  <si>
-    <t>Solange Noriega</t>
-  </si>
-  <si>
-    <t>Juana Morey</t>
-  </si>
-  <si>
-    <t>Gianpiero Olaya</t>
-  </si>
-  <si>
-    <t>Sandra Alvarado</t>
-  </si>
-  <si>
-    <t>Patricia Tello</t>
-  </si>
-  <si>
-    <t>Silvia Saavedra</t>
-  </si>
-  <si>
-    <t>Isaac Coriat</t>
-  </si>
-  <si>
-    <t>Janeth Caballero</t>
-  </si>
-  <si>
-    <t>Liz Vargas</t>
-  </si>
-  <si>
-    <t>Isac Maldonado</t>
-  </si>
-  <si>
-    <t>Melina Marquilla</t>
-  </si>
-  <si>
-    <t>Janeth Escobar</t>
-  </si>
-  <si>
-    <t>Gilson  Amasifuen</t>
-  </si>
-  <si>
-    <t>Miguel Zurita</t>
-  </si>
-  <si>
-    <t>Sliver Ramirez</t>
-  </si>
-  <si>
-    <t>Erick Melendez</t>
-  </si>
-  <si>
-    <t>Joaquim Villareal</t>
-  </si>
-  <si>
-    <t>Fabrizzio Marin</t>
-  </si>
-  <si>
-    <t>Adolfo Arevalo</t>
-  </si>
-  <si>
-    <t>Joaquim Flores</t>
-  </si>
-  <si>
-    <t>Elva Ruiz</t>
-  </si>
-  <si>
-    <t>Angel Cuya</t>
-  </si>
-  <si>
-    <t>Marino Lozano</t>
-  </si>
-  <si>
-    <t>Chepita Mori</t>
-  </si>
-  <si>
-    <t>Paquita Lozano</t>
-  </si>
-  <si>
-    <t>Kiler Coral</t>
-  </si>
-  <si>
-    <t>Luis Rios Trigozo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erika Garcia Ramirez </t>
-  </si>
-  <si>
-    <t>Alexia Rios Garcia</t>
-  </si>
-  <si>
-    <t>Omar Murillo</t>
-  </si>
-  <si>
-    <t>Tricia Garcia Ramirez</t>
-  </si>
-  <si>
-    <t>Jose Luis Garcia Ramirez</t>
-  </si>
-  <si>
-    <t>Malena Orosco La Vera, Maria Alejandra Garcia Orosco</t>
-  </si>
-  <si>
-    <t>Alonso Garcia Orosco</t>
-  </si>
-  <si>
-    <t>Alessa Guerrero</t>
-  </si>
-  <si>
-    <t>Luis Garcia Hidalgo</t>
-  </si>
-  <si>
-    <t>Enith Ramirez Macedo</t>
-  </si>
-  <si>
-    <t>Gretty Garcia Hidalgo</t>
-  </si>
-  <si>
-    <t>Grace  Pérez Garcia</t>
-  </si>
-  <si>
-    <t>Lily Pérez Garcia</t>
-  </si>
-  <si>
-    <t>Abdellah Ammouri</t>
-  </si>
-  <si>
-    <t>Tatiana Pérez- Clement</t>
-  </si>
-  <si>
-    <t>Arnaud Clement</t>
-  </si>
-  <si>
-    <t>Teddy Ramirez Macedo</t>
-  </si>
-  <si>
-    <t>Julio Ramirez Macedo</t>
-  </si>
-  <si>
-    <t>Rosa Paredes Piña, Julio Abel Ramirez</t>
-  </si>
-  <si>
-    <t>Miguel Galvéz Tello</t>
-  </si>
-  <si>
-    <t>Margarita Rios Trigozo, Facundo Galvéz Rios</t>
-  </si>
-  <si>
-    <t>Camila Galvéz  Rios</t>
-  </si>
-  <si>
-    <t>Jorge Valdez</t>
-  </si>
-  <si>
-    <t>Jhonathan Hidalgo</t>
-  </si>
-  <si>
-    <t>Alessandra Galvéz Rios</t>
-  </si>
-  <si>
-    <t>Bruno Galvéz</t>
-  </si>
-  <si>
-    <t>Iraida Trigozo del Aguila</t>
-  </si>
-  <si>
-    <t>Carlos Rios Trigozo</t>
-  </si>
-  <si>
-    <t>Deysi Cortez Mendoza</t>
-  </si>
-  <si>
-    <t>Maria Elena Rios Trigozo</t>
-  </si>
-  <si>
-    <t>Diego Romero Rios, Lucia Romero Rios</t>
-  </si>
-  <si>
-    <t>Adrian Rios Rondona</t>
-  </si>
-  <si>
-    <t>Sheryl Medina</t>
-  </si>
-  <si>
-    <t>Luis Mori Reategui</t>
-  </si>
-  <si>
-    <t>Liz Cheril Torres Reategui</t>
-  </si>
-  <si>
-    <t>Alison Mori</t>
-  </si>
-  <si>
-    <t>Giovanni Ponce Saavedra</t>
-  </si>
-  <si>
-    <t>Jessica Chong , Carlos Ponce Chong</t>
-  </si>
-  <si>
-    <t>Pamela Chu Noriega</t>
-  </si>
-  <si>
-    <t>Ivana Mendoza, Valeria Mendoza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Mendoza </t>
-  </si>
-  <si>
-    <t>Percy Ponce Saavedra</t>
-  </si>
-  <si>
-    <t>Gretell Romero</t>
-  </si>
-  <si>
-    <t>Jorge Rios Hoyos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Canani </t>
-  </si>
-  <si>
-    <t>Jesus Enrique Arevalo</t>
-  </si>
-  <si>
-    <t>Karen Documet, Joaquim Arevalo</t>
-  </si>
-  <si>
-    <t>Fernando Tafur</t>
-  </si>
-  <si>
-    <t>Alfredo Kong</t>
-  </si>
-  <si>
-    <t>Rosa Chin Chau</t>
-  </si>
-  <si>
-    <t>Lluis Dalmau</t>
-  </si>
-  <si>
-    <t>Lluis Dalmau Mendoza, Quim Dalmau Mendoza, Ariadna Dalmau Mendoza</t>
-  </si>
-  <si>
-    <t>Moi Merino Morey</t>
-  </si>
-  <si>
-    <t>Carmen Padilla</t>
-  </si>
-  <si>
-    <t>Rolando Lam</t>
-  </si>
-  <si>
-    <t>Milagros Gardini</t>
-  </si>
-  <si>
-    <t>Tato Reategui</t>
-  </si>
-  <si>
-    <t>Violeta Cortez, Alexandra Reategui, Gianluca Reategui</t>
-  </si>
-  <si>
-    <t>Nancy Macedo</t>
-  </si>
-  <si>
-    <t>Lucecita Pretell</t>
-  </si>
-  <si>
-    <t>Talita Garcia</t>
-  </si>
-  <si>
-    <t>Marlon Olortegui Peralta</t>
-  </si>
-  <si>
-    <t>Blanca Diaz</t>
-  </si>
-  <si>
-    <t>Carlos Toribio</t>
-  </si>
-  <si>
-    <t>Julia Elvira</t>
-  </si>
-  <si>
-    <t>Carlos Santillán</t>
-  </si>
-  <si>
-    <t>Estephany Mori</t>
-  </si>
-  <si>
-    <t>Daniel Vásquez</t>
-  </si>
-  <si>
-    <t>Valentina Mesias</t>
-  </si>
-  <si>
-    <t>Diego Santillan</t>
-  </si>
-  <si>
-    <t>Juliana Segura</t>
-  </si>
-  <si>
-    <t>Samantha Zavaleta</t>
-  </si>
-  <si>
-    <t>Oscar Calderon</t>
-  </si>
-  <si>
-    <t>Frank Gonzales</t>
-  </si>
-  <si>
-    <t>Cinthya Palomino</t>
-  </si>
-  <si>
-    <t>Pedro Quiquen</t>
-  </si>
-  <si>
-    <t>Carolina Tuesta</t>
-  </si>
-  <si>
-    <t>Martin Sangama</t>
-  </si>
-  <si>
-    <t>Valerie Saire</t>
-  </si>
-  <si>
-    <t>Irving Espinoza</t>
-  </si>
-  <si>
-    <t>Samir Florian</t>
-  </si>
-  <si>
-    <t>Gabriel Mazzini</t>
-  </si>
-  <si>
-    <t>Alejandro Medina</t>
-  </si>
-  <si>
-    <t>Hilka Perez</t>
-  </si>
-  <si>
-    <t>Rodrigo Carrasco</t>
-  </si>
-  <si>
-    <t>Flavia Vega</t>
-  </si>
-  <si>
-    <t>Renzo Perez Rosas</t>
-  </si>
-  <si>
-    <t>Nicolas Valle</t>
-  </si>
-  <si>
-    <t>Renata Rojo</t>
-  </si>
-  <si>
-    <t>César Ramos</t>
-  </si>
-  <si>
-    <t>César Espinoza</t>
-  </si>
-  <si>
-    <t>Valeria Valles</t>
-  </si>
-  <si>
-    <t>Renato Fernandini</t>
-  </si>
-  <si>
-    <t>Fernanda Cárdenas</t>
-  </si>
-  <si>
-    <t>Lucia Rojas</t>
-  </si>
-  <si>
-    <t>Milagros Arevalo</t>
-  </si>
-  <si>
-    <t>Esteban Obed</t>
-  </si>
-  <si>
-    <t>Nicole Alarcon</t>
-  </si>
-  <si>
-    <t>Pierre Barté</t>
-  </si>
-  <si>
-    <t>Melissa Garfias</t>
-  </si>
-  <si>
-    <t>Jordy Pereira</t>
-  </si>
-  <si>
-    <t>Shania Alarcón</t>
-  </si>
-  <si>
-    <t>Mario Arroyo</t>
-  </si>
-  <si>
-    <t>Brigitte Stamenovic</t>
-  </si>
-  <si>
-    <t>Sebastian Salazar</t>
-  </si>
-  <si>
-    <t>Valerie Stamenovic</t>
-  </si>
-  <si>
-    <t>Javier Gómez Bustamante</t>
-  </si>
-  <si>
-    <t>Linda Sangama</t>
-  </si>
-  <si>
-    <t>Javier Romo</t>
-  </si>
-  <si>
-    <t>Nicolas Ramos</t>
-  </si>
-  <si>
-    <t>Juan Diego Diaz Grandez</t>
-  </si>
-  <si>
-    <t>Michelle Ponce Chong</t>
-  </si>
-  <si>
-    <t>Maximilian Kadzioch</t>
-  </si>
-  <si>
-    <t>Claudia Silva Estrada</t>
-  </si>
-  <si>
-    <t>Fiorella Rodriguez Sandoval</t>
-  </si>
-  <si>
-    <t>Silvia Rios Gil</t>
-  </si>
-  <si>
-    <t>Luciana Fajardo Sandy</t>
-  </si>
-  <si>
-    <t>Nicolle Ramirez Santillana</t>
-  </si>
-  <si>
-    <t>Melanie del Castillo</t>
-  </si>
-  <si>
-    <t>Alejandra Castillo</t>
-  </si>
-  <si>
-    <t>Rodrigo Amasifuen</t>
-  </si>
-  <si>
-    <t>Luis Angel Samaniego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro Lara </t>
-  </si>
-  <si>
-    <t>Fabrizzio Rios Canani</t>
-  </si>
-  <si>
-    <t>Leslie Arce</t>
-  </si>
-  <si>
-    <t>Sebastián Diaz Quiñe</t>
-  </si>
-  <si>
-    <t>Stefano Saracco Reategui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeria Aguirre </t>
-  </si>
-  <si>
-    <t>Claudia Morán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrea Villareal </t>
-  </si>
-  <si>
-    <t>Juan Alejandro Gomez</t>
-  </si>
-  <si>
-    <t>Jimena Calmet</t>
-  </si>
-  <si>
-    <t>Fernanda Linares</t>
-  </si>
-  <si>
-    <t>Adriana Linares</t>
-  </si>
-  <si>
-    <t>Axel Quiñe</t>
-  </si>
-  <si>
-    <t>Karla Rubio</t>
-  </si>
-  <si>
-    <t>Valentina Ponce Romero</t>
-  </si>
-  <si>
-    <t>Lucas Camargo</t>
-  </si>
-  <si>
-    <t>Andrea Ponce Romero</t>
-  </si>
-  <si>
-    <t>Jin Saldaña Kanan</t>
-  </si>
-  <si>
-    <t>Marcia Chavez</t>
-  </si>
-  <si>
-    <t>Fabio Guitierrez</t>
-  </si>
-  <si>
-    <t>Mariana Loli</t>
-  </si>
-  <si>
-    <t>Valeria Sotelo</t>
-  </si>
-  <si>
-    <t>Mauricio Fernandez</t>
-  </si>
-  <si>
-    <t>Joseph Trigozo</t>
-  </si>
-  <si>
-    <t>Renzo Reategui Rey</t>
-  </si>
-  <si>
-    <t>Brenda Pedreschi</t>
-  </si>
-  <si>
-    <t>Miguel Angel Wong</t>
-  </si>
-  <si>
-    <t>Alonso Mansilla</t>
-  </si>
-  <si>
-    <t>Mario Berghusen</t>
-  </si>
-  <si>
-    <t>Mauricio Choy</t>
-  </si>
-  <si>
-    <t>Sebastian Saz</t>
-  </si>
-  <si>
-    <t>Florencia Hung</t>
-  </si>
-  <si>
-    <t>Vanessa Vergara</t>
-  </si>
-  <si>
-    <t>Bryan Gonzales</t>
-  </si>
-  <si>
-    <t>Gisella  Pinedo</t>
-  </si>
-  <si>
-    <t>Rossana Corzano</t>
-  </si>
-  <si>
-    <t>Ivan Alarcon</t>
-  </si>
-  <si>
-    <t>Mariana Bocanegra</t>
-  </si>
-  <si>
-    <t>Claudia Hermoza</t>
-  </si>
-  <si>
-    <t>Lucia Valdiviezo</t>
-  </si>
-  <si>
-    <t>Michelle Bergelund</t>
   </si>
 </sst>
 </file>
@@ -1145,12 +1147,24 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1159,7 +1173,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1170,6 +1184,21 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1425,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -1447,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -1455,7 +1484,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -1463,24 +1492,24 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C8" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
@@ -1499,18 +1528,18 @@
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3">
         <v>2.0</v>
@@ -1518,13 +1547,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -1543,18 +1572,18 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3">
         <v>1.0</v>
@@ -1562,10 +1591,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C16" s="3">
         <v>2.0</v>
@@ -1573,10 +1602,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3">
         <v>1.0</v>
@@ -1584,10 +1613,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C18" s="3">
         <v>2.0</v>
@@ -1595,10 +1624,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="C19" s="3">
         <v>2.0</v>
@@ -1606,21 +1635,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C20" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3">
         <v>2.0</v>
@@ -1628,98 +1657,104 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C22" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C23" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C26" s="3">
         <v>2.0</v>
       </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C27" s="3">
-        <v>1.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="3">
-        <v>1.0</v>
+      <c r="B28" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="3">
+      <c r="B29" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="6">
         <v>2.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" s="3">
         <v>2.0</v>
@@ -1727,10 +1762,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3">
         <v>2.0</v>
@@ -1738,10 +1773,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C32" s="3">
         <v>1.0</v>
@@ -1749,13 +1784,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C33" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="34">
@@ -1785,21 +1820,21 @@
         <v>61</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="C36" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C37" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="38">
@@ -1829,18 +1864,18 @@
         <v>68</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="C40" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C41" s="3">
         <v>1.0</v>
@@ -1848,32 +1883,32 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="C42" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C43" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C44" s="3">
         <v>2.0</v>
@@ -1881,21 +1916,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C45" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C46" s="3">
         <v>1.0</v>
@@ -1903,10 +1938,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C47" s="3">
         <v>2.0</v>
@@ -1914,21 +1949,21 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C48" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3">
         <v>2.0</v>
@@ -1936,10 +1971,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C50" s="3">
         <v>2.0</v>
@@ -1947,10 +1982,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C51" s="3">
         <v>2.0</v>
@@ -1958,21 +1993,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="C52" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C53" s="3">
         <v>2.0</v>
@@ -1980,21 +2015,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C55" s="3">
         <v>2.0</v>
@@ -2002,10 +2037,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C56" s="3">
         <v>2.0</v>
@@ -2013,10 +2048,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C57" s="3">
         <v>2.0</v>
@@ -2024,10 +2059,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C58" s="3">
         <v>1.0</v>
@@ -2035,21 +2070,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="C59" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C60" s="3">
         <v>1.0</v>
@@ -2057,10 +2092,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C61" s="3">
         <v>2.0</v>
@@ -2068,21 +2103,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="C62" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C63" s="3">
         <v>2.0</v>
@@ -2090,10 +2125,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C64" s="3">
         <v>2.0</v>
@@ -2101,19 +2136,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B65" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C65" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="C66" s="3">
         <v>2.0</v>
@@ -2121,21 +2158,21 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="C67" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C68" s="3">
         <v>2.0</v>
@@ -2143,21 +2180,21 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C69" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="C70" s="3">
         <v>2.0</v>
@@ -2165,10 +2202,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C71" s="3">
         <v>1.0</v>
@@ -2176,10 +2213,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3">
         <v>2.0</v>
@@ -2187,43 +2224,43 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="C73" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="C74" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="C75" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C76" s="3">
         <v>2.0</v>
@@ -2231,21 +2268,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C77" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C78" s="3">
         <v>1.0</v>
@@ -2253,10 +2290,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C79" s="3">
         <v>2.0</v>
@@ -2264,10 +2301,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C80" s="3">
         <v>2.0</v>
@@ -2275,10 +2312,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C81" s="3">
         <v>1.0</v>
@@ -2286,10 +2323,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C82" s="3">
         <v>2.0</v>
@@ -2297,10 +2334,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C83" s="3">
         <v>1.0</v>
@@ -2308,21 +2345,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C84" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C85" s="3">
         <v>1.0</v>
@@ -2330,65 +2367,65 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C86" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="C87" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="C88" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C89" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>152</v>
+        <v>6</v>
       </c>
       <c r="C90" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C91" s="3">
         <v>2.0</v>
@@ -2396,32 +2433,32 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="C92" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="C93" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C94" s="3">
         <v>2.0</v>
@@ -2429,10 +2466,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="C95" s="3">
         <v>2.0</v>
@@ -2440,21 +2477,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="C96" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C97" s="3">
         <v>2.0</v>
@@ -2462,10 +2499,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C98" s="3">
         <v>2.0</v>
@@ -2473,10 +2510,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C99" s="3">
         <v>2.0</v>
@@ -2484,32 +2521,32 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
       <c r="C100" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C101" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C102" s="3">
         <v>1.0</v>
@@ -2517,10 +2554,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C103" s="3">
         <v>2.0</v>
@@ -2528,10 +2565,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C104" s="3">
         <v>2.0</v>
@@ -2539,32 +2576,32 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>180</v>
+        <v>6</v>
       </c>
       <c r="C105" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C106" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="C107" s="3">
         <v>2.0</v>
@@ -2572,43 +2609,43 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="C108" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="C109" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="C110" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C111" s="3">
         <v>2.0</v>
@@ -2616,10 +2653,10 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C112" s="3">
         <v>2.0</v>
@@ -2627,21 +2664,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="C113" s="3">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="C114" s="3">
         <v>2.0</v>
@@ -2649,21 +2686,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="C115" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C116" s="3">
         <v>1.0</v>
@@ -2671,10 +2708,10 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C117" s="3">
         <v>1.0</v>
@@ -2682,10 +2719,10 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C118" s="3">
         <v>1.0</v>
@@ -2693,10 +2730,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C119" s="3">
         <v>1.0</v>
@@ -2704,10 +2741,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C120" s="3">
         <v>1.0</v>
@@ -2715,35 +2752,35 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>12</v>
+        <v>195</v>
       </c>
       <c r="C121" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="C122" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C123" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -2751,18 +2788,18 @@
         <v>200</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>201</v>
+        <v>6</v>
       </c>
       <c r="C124" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="C125" s="3">
         <v>2.0</v>
@@ -2770,10 +2807,10 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="C126" s="3">
         <v>2.0</v>
@@ -2781,21 +2818,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>207</v>
+        <v>6</v>
       </c>
       <c r="C127" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C128" s="3">
         <v>2.0</v>
@@ -2803,32 +2840,32 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="C129" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="C130" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="C131" s="3">
         <v>2.0</v>
@@ -2836,10 +2873,10 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C132" s="3">
         <v>2.0</v>
@@ -2847,10 +2884,10 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C133" s="3">
         <v>1.0</v>
@@ -2858,10 +2895,10 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C134" s="3">
         <v>2.0</v>
@@ -2875,7 +2912,7 @@
         <v>220</v>
       </c>
       <c r="C135" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="136">
@@ -2883,18 +2920,18 @@
         <v>221</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>222</v>
+        <v>6</v>
       </c>
       <c r="C136" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C137" s="3">
         <v>1.0</v>
@@ -2902,65 +2939,65 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="C138" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C139" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>229</v>
+        <v>6</v>
       </c>
       <c r="C140" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>231</v>
+        <v>6</v>
       </c>
       <c r="C141" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>12</v>
+        <v>229</v>
       </c>
       <c r="C142" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C143" s="3">
         <v>1.0</v>
@@ -2968,43 +3005,43 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="C144" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>237</v>
+        <v>6</v>
       </c>
       <c r="C145" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>239</v>
+        <v>6</v>
       </c>
       <c r="C146" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C147" s="3">
         <v>1.0</v>
@@ -3012,10 +3049,10 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>242</v>
+        <v>6</v>
       </c>
       <c r="C148" s="3">
         <v>2.0</v>
@@ -3023,43 +3060,43 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>244</v>
+        <v>6</v>
       </c>
       <c r="C149" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C150" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="C151" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C152" s="3">
         <v>2.0</v>
@@ -3067,43 +3104,41 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>251</v>
+        <v>6</v>
       </c>
       <c r="C153" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>253</v>
+        <v>6</v>
       </c>
       <c r="C154" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>12</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="B155" s="2"/>
       <c r="C155" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C156" s="3">
         <v>2.0</v>
@@ -3111,21 +3146,21 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>258</v>
+        <v>6</v>
       </c>
       <c r="C157" s="3">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C158" s="3">
         <v>2.0</v>
@@ -3133,10 +3168,10 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>262</v>
+        <v>6</v>
       </c>
       <c r="C159" s="3">
         <v>2.0</v>
@@ -3144,21 +3179,21 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>264</v>
+        <v>6</v>
       </c>
       <c r="C160" s="3">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>12</v>
+        <v>254</v>
       </c>
       <c r="C161" s="3">
         <v>2.0</v>
@@ -3166,21 +3201,21 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="C162" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C163" s="3">
         <v>2.0</v>
@@ -3188,21 +3223,21 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C164" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C165" s="3">
         <v>2.0</v>
@@ -3210,10 +3245,10 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>273</v>
+        <v>6</v>
       </c>
       <c r="C166" s="3">
         <v>2.0</v>
@@ -3221,43 +3256,43 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C167" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C168" s="3">
-        <v>2.0</v>
+      <c r="A168" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="8">
+        <v>1.0</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C169" s="3">
+      <c r="A169" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C169" s="8">
         <v>2.0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C170" s="3">
         <v>2.0</v>
@@ -3265,32 +3300,32 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C171" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="C172" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="C173" s="3">
         <v>2.0</v>
@@ -3298,10 +3333,10 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>12</v>
+        <v>275</v>
       </c>
       <c r="C174" s="3">
         <v>2.0</v>
@@ -3309,32 +3344,32 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C175" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>290</v>
+        <v>6</v>
       </c>
       <c r="C176" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="C177" s="3">
         <v>2.0</v>
@@ -3342,21 +3377,21 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>12</v>
+        <v>281</v>
       </c>
       <c r="C178" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C179" s="3">
         <v>2.0</v>
@@ -3364,21 +3399,21 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>12</v>
+        <v>285</v>
       </c>
       <c r="C180" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C181" s="3">
         <v>2.0</v>
@@ -3386,43 +3421,43 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="C182" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>12</v>
+        <v>290</v>
       </c>
       <c r="C183" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C184" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C185" s="3">
         <v>1.0</v>
@@ -3430,10 +3465,10 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="C186" s="3">
         <v>2.0</v>
@@ -3441,10 +3476,10 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C187" s="3">
         <v>2.0</v>
@@ -3452,32 +3487,32 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>308</v>
+        <v>6</v>
       </c>
       <c r="C188" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>12</v>
+        <v>299</v>
       </c>
       <c r="C189" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C190" s="3">
         <v>2.0</v>
@@ -3485,10 +3520,10 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C191" s="3">
         <v>2.0</v>
@@ -3496,21 +3531,21 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C192" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="C193" s="3">
         <v>2.0</v>
@@ -3518,21 +3553,21 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>12</v>
+        <v>309</v>
       </c>
       <c r="C194" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C195" s="3">
         <v>2.0</v>
@@ -3540,10 +3575,10 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>320</v>
+        <v>134</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C196" s="3">
         <v>1.0</v>
@@ -3551,10 +3586,10 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>12</v>
+        <v>313</v>
       </c>
       <c r="C197" s="3">
         <v>2.0</v>
@@ -3562,10 +3597,10 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>322</v>
+        <v>182</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C198" s="3">
         <v>1.0</v>
@@ -3573,32 +3608,32 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>12</v>
+        <v>315</v>
       </c>
       <c r="C199" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C200" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C201" s="3">
         <v>1.0</v>
@@ -3606,10 +3641,10 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C202" s="3">
         <v>2.0</v>
@@ -3617,21 +3652,21 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="C203" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C204" s="3">
         <v>1.0</v>
@@ -3639,54 +3674,54 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>331</v>
+        <v>6</v>
       </c>
       <c r="C205" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>12</v>
+        <v>325</v>
       </c>
       <c r="C206" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>12</v>
+        <v>327</v>
       </c>
       <c r="C207" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>12</v>
+        <v>329</v>
       </c>
       <c r="C208" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C209" s="3">
         <v>1.0</v>
@@ -3694,10 +3729,10 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C210" s="3">
         <v>1.0</v>
@@ -3705,32 +3740,32 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>338</v>
+        <v>6</v>
       </c>
       <c r="C211" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>340</v>
+        <v>6</v>
       </c>
       <c r="C212" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C213" s="3">
         <v>2.0</v>
@@ -3738,21 +3773,21 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>344</v>
+        <v>6</v>
       </c>
       <c r="C214" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C215" s="3">
         <v>1.0</v>
@@ -3760,65 +3795,65 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>12</v>
+        <v>339</v>
       </c>
       <c r="C216" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>12</v>
+        <v>341</v>
       </c>
       <c r="C217" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C218" s="3">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>351</v>
+        <v>6</v>
       </c>
       <c r="C219" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>12</v>
+        <v>346</v>
       </c>
       <c r="C220" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C221" s="3">
         <v>1.0</v>
@@ -3826,10 +3861,10 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C222" s="3">
         <v>2.0</v>
@@ -3837,10 +3872,10 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C223" s="3">
         <v>1.0</v>
@@ -3848,10 +3883,10 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C224" s="3">
         <v>1.0</v>
@@ -3859,76 +3894,76 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>12</v>
+        <v>353</v>
       </c>
       <c r="C225" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>12</v>
+        <v>355</v>
       </c>
       <c r="C226" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>12</v>
+        <v>357</v>
       </c>
       <c r="C227" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>12</v>
+        <v>359</v>
       </c>
       <c r="C228" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>363</v>
+        <v>6</v>
       </c>
       <c r="C229" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>365</v>
+        <v>6</v>
       </c>
       <c r="C230" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>12</v>
+        <v>363</v>
       </c>
       <c r="C231" s="3">
         <v>2.0</v>
@@ -3936,38 +3971,43 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>12</v>
+        <v>365</v>
       </c>
       <c r="C232" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>12</v>
+        <v>367</v>
       </c>
       <c r="C233" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B234" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C234" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="$A$1:$C$234">
+    <sortState ref="A1:C234">
+      <sortCondition ref="A1:A234"/>
+    </sortState>
+  </autoFilter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/danielaybruno/danielaybruno.xlsx
+++ b/danielaybruno/danielaybruno.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$C$234</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$C$233</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="371">
   <si>
     <t>Nombre Completo</t>
   </si>
@@ -162,7 +162,7 @@
     <t>Karina Sanchez</t>
   </si>
   <si>
-    <t>Carlos Santillán</t>
+    <t>Carlos Santillán Sánchez</t>
   </si>
   <si>
     <t>Estephany Mori</t>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>Carolina Gomez</t>
+  </si>
+  <si>
+    <t>Oscar Gómez</t>
   </si>
   <si>
     <t>Cesar Cucho</t>
@@ -1173,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1195,8 +1198,14 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1709,9 +1718,6 @@
       <c r="C26" s="3">
         <v>2.0</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
@@ -1723,9 +1729,6 @@
       <c r="C27" s="3">
         <v>2.0</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
@@ -1739,7 +1742,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B29" s="5" t="s">
@@ -1783,22 +1786,22 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="3">
+      <c r="B33" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="10">
         <v>1.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" s="3">
         <v>2.0</v>
@@ -1806,10 +1809,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C35" s="3">
         <v>2.0</v>
@@ -1817,7 +1820,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>6</v>
@@ -1828,10 +1831,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C37" s="3">
         <v>2.0</v>
@@ -1839,10 +1842,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C38" s="3">
         <v>2.0</v>
@@ -1850,10 +1853,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C39" s="3">
         <v>2.0</v>
@@ -1861,7 +1864,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>6</v>
@@ -1872,7 +1875,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>6</v>
@@ -1883,7 +1886,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>6</v>
@@ -1894,7 +1897,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>6</v>
@@ -1905,10 +1908,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C44" s="3">
         <v>2.0</v>
@@ -1916,10 +1919,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C45" s="3">
         <v>2.0</v>
@@ -1927,7 +1930,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>6</v>
@@ -1938,10 +1941,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C47" s="3">
         <v>2.0</v>
@@ -1949,10 +1952,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C48" s="3">
         <v>3.0</v>
@@ -1960,10 +1963,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C49" s="3">
         <v>2.0</v>
@@ -1971,10 +1974,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C50" s="3">
         <v>2.0</v>
@@ -1982,10 +1985,10 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C51" s="3">
         <v>2.0</v>
@@ -1993,7 +1996,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>6</v>
@@ -2004,10 +2007,10 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" s="3">
         <v>2.0</v>
@@ -2015,7 +2018,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>6</v>
@@ -2026,10 +2029,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C55" s="3">
         <v>2.0</v>
@@ -2037,10 +2040,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C56" s="3">
         <v>2.0</v>
@@ -2048,10 +2051,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C57" s="3">
         <v>2.0</v>
@@ -2059,7 +2062,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>6</v>
@@ -2070,7 +2073,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>6</v>
@@ -2081,7 +2084,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>6</v>
@@ -2092,10 +2095,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C61" s="3">
         <v>2.0</v>
@@ -2103,7 +2106,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>6</v>
@@ -2114,10 +2117,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C63" s="3">
         <v>2.0</v>
@@ -2125,10 +2128,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C64" s="3">
         <v>2.0</v>
@@ -2136,7 +2139,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>6</v>
@@ -2147,7 +2150,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>6</v>
@@ -2158,7 +2161,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>6</v>
@@ -2169,10 +2172,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C68" s="3">
         <v>2.0</v>
@@ -2180,10 +2183,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C69" s="3">
         <v>2.0</v>
@@ -2191,7 +2194,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>6</v>
@@ -2202,7 +2205,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>6</v>
@@ -2213,7 +2216,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>6</v>
@@ -2224,7 +2227,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>6</v>
@@ -2235,10 +2238,10 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C74" s="3">
         <v>3.0</v>
@@ -2246,7 +2249,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>6</v>
@@ -2257,10 +2260,10 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C76" s="3">
         <v>2.0</v>
@@ -2268,7 +2271,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>6</v>
@@ -2279,7 +2282,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>6</v>
@@ -2290,10 +2293,10 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C79" s="3">
         <v>2.0</v>
@@ -2301,10 +2304,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C80" s="3">
         <v>2.0</v>
@@ -2312,7 +2315,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>6</v>
@@ -2323,10 +2326,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C82" s="3">
         <v>2.0</v>
@@ -2334,7 +2337,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>6</v>
@@ -2345,10 +2348,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C84" s="3">
         <v>2.0</v>
@@ -2356,7 +2359,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>6</v>
@@ -2367,7 +2370,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>6</v>
@@ -2378,10 +2381,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C87" s="3">
         <v>2.0</v>
@@ -2389,10 +2392,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C88" s="3">
         <v>3.0</v>
@@ -2400,10 +2403,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C89" s="3">
         <v>2.0</v>
@@ -2411,7 +2414,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>6</v>
@@ -2422,10 +2425,10 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C91" s="3">
         <v>2.0</v>
@@ -2433,7 +2436,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>6</v>
@@ -2444,7 +2447,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>6</v>
@@ -2455,10 +2458,10 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C94" s="3">
         <v>2.0</v>
@@ -2466,10 +2469,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C95" s="3">
         <v>2.0</v>
@@ -2477,10 +2480,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C96" s="3">
         <v>2.0</v>
@@ -2488,10 +2491,10 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C97" s="3">
         <v>2.0</v>
@@ -2499,10 +2502,10 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C98" s="3">
         <v>2.0</v>
@@ -2510,10 +2513,10 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C99" s="3">
         <v>2.0</v>
@@ -2521,7 +2524,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>6</v>
@@ -2532,10 +2535,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C101" s="3">
         <v>3.0</v>
@@ -2543,7 +2546,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>6</v>
@@ -2554,10 +2557,10 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C103" s="3">
         <v>2.0</v>
@@ -2565,10 +2568,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C104" s="3">
         <v>2.0</v>
@@ -2576,7 +2579,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>6</v>
@@ -2587,10 +2590,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C106" s="3">
         <v>3.0</v>
@@ -2598,10 +2601,10 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C107" s="3">
         <v>2.0</v>
@@ -2609,10 +2612,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C108" s="3">
         <v>2.0</v>
@@ -2620,10 +2623,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C109" s="3">
         <v>2.0</v>
@@ -2631,10 +2634,10 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C110" s="3">
         <v>2.0</v>
@@ -2642,10 +2645,10 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C111" s="3">
         <v>2.0</v>
@@ -2653,10 +2656,10 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C112" s="3">
         <v>2.0</v>
@@ -2664,10 +2667,10 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C113" s="3">
         <v>4.0</v>
@@ -2675,10 +2678,10 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C114" s="3">
         <v>2.0</v>
@@ -2686,10 +2689,10 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C115" s="3">
         <v>2.0</v>
@@ -2697,7 +2700,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>6</v>
@@ -2708,7 +2711,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>6</v>
@@ -2719,7 +2722,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>6</v>
@@ -2730,7 +2733,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>6</v>
@@ -2741,7 +2744,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>6</v>
@@ -2752,10 +2755,10 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C121" s="3">
         <v>2.0</v>
@@ -2763,10 +2766,10 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C122" s="3">
         <v>2.0</v>
@@ -2774,10 +2777,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C123" s="3">
         <v>2.0</v>
@@ -2785,7 +2788,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>6</v>
@@ -2796,10 +2799,10 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C125" s="3">
         <v>2.0</v>
@@ -2807,10 +2810,10 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C126" s="3">
         <v>2.0</v>
@@ -2818,7 +2821,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>6</v>
@@ -2829,10 +2832,10 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C128" s="3">
         <v>2.0</v>
@@ -2840,10 +2843,10 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C129" s="3">
         <v>2.0</v>
@@ -2851,10 +2854,10 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C130" s="3">
         <v>2.0</v>
@@ -2862,10 +2865,10 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C131" s="3">
         <v>2.0</v>
@@ -2873,10 +2876,10 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C132" s="3">
         <v>2.0</v>
@@ -2884,7 +2887,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>6</v>
@@ -2895,10 +2898,10 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C134" s="3">
         <v>2.0</v>
@@ -2906,10 +2909,10 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C135" s="3">
         <v>3.0</v>
@@ -2917,7 +2920,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>6</v>
@@ -2928,7 +2931,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>6</v>
@@ -2939,7 +2942,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>6</v>
@@ -2950,10 +2953,10 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C139" s="3">
         <v>2.0</v>
@@ -2961,7 +2964,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>6</v>
@@ -2972,7 +2975,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>6</v>
@@ -2983,10 +2986,10 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C142" s="3">
         <v>2.0</v>
@@ -2994,7 +2997,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>6</v>
@@ -3005,7 +3008,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>6</v>
@@ -3016,7 +3019,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>6</v>
@@ -3027,7 +3030,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>6</v>
@@ -3038,7 +3041,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>6</v>
@@ -3049,7 +3052,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>6</v>
@@ -3060,7 +3063,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>6</v>
@@ -3071,10 +3074,10 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C150" s="3">
         <v>2.0</v>
@@ -3082,10 +3085,10 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C151" s="3">
         <v>3.0</v>
@@ -3093,10 +3096,10 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C152" s="3">
         <v>2.0</v>
@@ -3104,7 +3107,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>6</v>
@@ -3115,7 +3118,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>6</v>
@@ -3126,7 +3129,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B155" s="2"/>
       <c r="C155" s="3">
@@ -3135,10 +3138,10 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C156" s="3">
         <v>2.0</v>
@@ -3146,7 +3149,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>6</v>
@@ -3157,10 +3160,10 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C158" s="3">
         <v>2.0</v>
@@ -3168,7 +3171,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>6</v>
@@ -3179,7 +3182,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>6</v>
@@ -3190,10 +3193,10 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C161" s="3">
         <v>2.0</v>
@@ -3201,10 +3204,10 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C162" s="3">
         <v>3.0</v>
@@ -3212,10 +3215,10 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C163" s="3">
         <v>2.0</v>
@@ -3223,7 +3226,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>6</v>
@@ -3234,10 +3237,10 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C165" s="3">
         <v>2.0</v>
@@ -3245,7 +3248,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>6</v>
@@ -3256,7 +3259,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>6</v>
@@ -3266,55 +3269,55 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C168" s="8">
-        <v>1.0</v>
+      <c r="A168" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C168" s="10">
+        <v>2.0</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C169" s="8">
+      <c r="A169" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C169" s="3">
         <v>2.0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C170" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C171" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C172" s="3">
         <v>2.0</v>
@@ -3322,10 +3325,10 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C173" s="3">
         <v>2.0</v>
@@ -3333,18 +3336,18 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C174" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>6</v>
@@ -3355,21 +3358,21 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>6</v>
+        <v>280</v>
       </c>
       <c r="C176" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C177" s="3">
         <v>2.0</v>
@@ -3377,10 +3380,10 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C178" s="3">
         <v>2.0</v>
@@ -3388,10 +3391,10 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C179" s="3">
         <v>2.0</v>
@@ -3399,10 +3402,10 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C180" s="3">
         <v>2.0</v>
@@ -3410,40 +3413,40 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>287</v>
+        <v>6</v>
       </c>
       <c r="C181" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>6</v>
+        <v>291</v>
       </c>
       <c r="C182" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>290</v>
+        <v>6</v>
       </c>
       <c r="C183" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>6</v>
@@ -3454,21 +3457,21 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>6</v>
+        <v>295</v>
       </c>
       <c r="C185" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C186" s="3">
         <v>2.0</v>
@@ -3476,32 +3479,32 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>296</v>
+        <v>6</v>
       </c>
       <c r="C187" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="C188" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C189" s="3">
         <v>2.0</v>
@@ -3509,10 +3512,10 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C190" s="3">
         <v>2.0</v>
@@ -3520,32 +3523,32 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C191" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C192" s="3">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C193" s="3">
         <v>2.0</v>
@@ -3553,10 +3556,10 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C194" s="3">
         <v>2.0</v>
@@ -3564,54 +3567,54 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>311</v>
+        <v>6</v>
       </c>
       <c r="C195" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>134</v>
+        <v>313</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>6</v>
+        <v>314</v>
       </c>
       <c r="C196" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>312</v>
+        <v>183</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>313</v>
+        <v>6</v>
       </c>
       <c r="C197" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>182</v>
+        <v>315</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>6</v>
+        <v>316</v>
       </c>
       <c r="C198" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>315</v>
+        <v>6</v>
       </c>
       <c r="C199" s="3">
         <v>2.0</v>
@@ -3619,51 +3622,51 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C200" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="C201" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C202" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>321</v>
+        <v>6</v>
       </c>
       <c r="C203" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>6</v>
@@ -3674,21 +3677,21 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>6</v>
+        <v>326</v>
       </c>
       <c r="C205" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C206" s="3">
         <v>2.0</v>
@@ -3696,10 +3699,10 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C207" s="3">
         <v>2.0</v>
@@ -3707,18 +3710,18 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>329</v>
+        <v>6</v>
       </c>
       <c r="C208" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>6</v>
@@ -3729,7 +3732,7 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>6</v>
@@ -3740,7 +3743,7 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>6</v>
@@ -3751,29 +3754,29 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>6</v>
+        <v>336</v>
       </c>
       <c r="C212" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>335</v>
+        <v>6</v>
       </c>
       <c r="C213" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>6</v>
@@ -3784,21 +3787,21 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>6</v>
+        <v>340</v>
       </c>
       <c r="C215" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C216" s="3">
         <v>2.0</v>
@@ -3806,73 +3809,73 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C217" s="3">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>343</v>
+        <v>6</v>
       </c>
       <c r="C218" s="3">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>6</v>
+        <v>347</v>
       </c>
       <c r="C219" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>346</v>
+        <v>6</v>
       </c>
       <c r="C220" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>6</v>
+        <v>350</v>
       </c>
       <c r="C221" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>349</v>
+        <v>6</v>
       </c>
       <c r="C222" s="3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>6</v>
@@ -3883,21 +3886,21 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>6</v>
+        <v>354</v>
       </c>
       <c r="C224" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C225" s="3">
         <v>2.0</v>
@@ -3905,10 +3908,10 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C226" s="3">
         <v>2.0</v>
@@ -3916,29 +3919,29 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C227" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>359</v>
+        <v>6</v>
       </c>
       <c r="C228" s="3">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>6</v>
@@ -3949,21 +3952,21 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>6</v>
+        <v>364</v>
       </c>
       <c r="C230" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C231" s="3">
         <v>2.0</v>
@@ -3971,10 +3974,10 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C232" s="3">
         <v>2.0</v>
@@ -3982,30 +3985,19 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C233" s="3">
         <v>2.0</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C234" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$C$234">
-    <sortState ref="A1:C234">
-      <sortCondition ref="A1:A234"/>
+  <autoFilter ref="$A$1:$C$233">
+    <sortState ref="A1:C233">
+      <sortCondition ref="A1:A233"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
